--- a/MU/Test upload format/Normal/2026 - 2027/CP2 26-27.xlsx
+++ b/MU/Test upload format/Normal/2026 - 2027/CP2 26-27.xlsx
@@ -4,11 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180"/>
+    <workbookView windowWidth="24000" windowHeight="9600"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$T$8</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -27,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="40">
   <si>
     <t>custid</t>
   </si>
@@ -86,22 +89,67 @@
     <t>modifiedloancat</t>
   </si>
   <si>
-    <t>Envv09</t>
-  </si>
-  <si>
-    <t>Envv10</t>
+    <t>HomeStay</t>
+  </si>
+  <si>
+    <t>Q2CR1503</t>
+  </si>
+  <si>
+    <t>50000</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>01-04-2026</t>
+    <t>40000</t>
+  </si>
+  <si>
+    <t>01-07-2026</t>
+  </si>
+  <si>
+    <t>1000000</t>
   </si>
   <si>
     <t>Y</t>
   </si>
   <si>
     <t>TP</t>
+  </si>
+  <si>
+    <t>Q2CR1506</t>
+  </si>
+  <si>
+    <t>Q2CR1509</t>
+  </si>
+  <si>
+    <t>Q2CR1512</t>
+  </si>
+  <si>
+    <t>01-08-2026</t>
+  </si>
+  <si>
+    <t>Q2CR1515</t>
+  </si>
+  <si>
+    <t>Q2CR1521</t>
+  </si>
+  <si>
+    <t>IA</t>
+  </si>
+  <si>
+    <t>10-08-2026</t>
+  </si>
+  <si>
+    <t>500000</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>Q2CR1524</t>
+  </si>
+  <si>
+    <t>2000001</t>
   </si>
 </sst>
 </file>
@@ -114,7 +162,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -131,12 +179,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -281,7 +323,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -290,7 +332,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.4"/>
+        <fgColor theme="5" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -481,7 +535,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -501,21 +555,6 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -637,70 +676,64 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -709,10 +742,10 @@
     <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -721,10 +754,10 @@
     <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -733,10 +766,10 @@
     <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -745,10 +778,10 @@
     <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -757,21 +790,30 @@
     <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -782,12 +824,17 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1321,8 +1368,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S2"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="1"/>
+  <dimension ref="A1:T8"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="27.4285714285714" customWidth="1"/>
     <col min="2" max="2" width="26.8571428571429" customWidth="1"/>
@@ -1333,116 +1380,421 @@
     <col min="7" max="7" width="20.2857142857143" customWidth="1"/>
     <col min="8" max="8" width="21.8571428571429" customWidth="1"/>
     <col min="9" max="9" width="19.2857142857143" customWidth="1"/>
+    <col min="12" max="12" width="12.7142857142857" customWidth="1"/>
+    <col min="13" max="13" width="19.5714285714286" customWidth="1"/>
     <col min="14" max="14" width="15.5714285714286" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:19">
-      <c r="A1" s="2" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:20">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="P1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="Q1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="R1" s="6" t="s">
         <v>17</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="2" spans="1:19">
-      <c r="A2" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="6" t="s">
+    <row r="2" spans="1:20">
+      <c r="A2" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="6">
-        <v>1000</v>
-      </c>
-      <c r="D2" s="7" t="s">
+      <c r="B2" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="6">
-        <v>9000</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>22</v>
+      <c r="D2" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="7">
+        <v>0</v>
+      </c>
+      <c r="L2" s="7">
+        <v>1</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="S2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20">
+      <c r="A3" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="K2" s="9">
+      <c r="D3" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" s="7">
         <v>0</v>
       </c>
-      <c r="L2" s="9">
+      <c r="L3" s="7">
         <v>1</v>
       </c>
-      <c r="M2" s="6">
-        <v>100000</v>
-      </c>
-      <c r="N2" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="P2" s="1" t="s">
+      <c r="M3" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="S3" t="s">
+        <v>27</v>
+      </c>
+      <c r="T3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20">
+      <c r="A4" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="G4" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" s="7">
+        <v>0</v>
+      </c>
+      <c r="L4" s="7">
+        <v>1</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="S4" t="s">
+        <v>27</v>
+      </c>
+      <c r="T4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20">
+      <c r="A5" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="G5" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K5" s="7">
+        <v>0</v>
+      </c>
+      <c r="L5" s="7">
+        <v>1</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="N5" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="S5" t="s">
+        <v>27</v>
+      </c>
+      <c r="T5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20">
+      <c r="A6" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="S2" t="s">
-        <v>24</v>
+      <c r="D6" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" s="7">
+        <v>0</v>
+      </c>
+      <c r="L6" s="7">
+        <v>1</v>
+      </c>
+      <c r="M6" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="S6" t="s">
+        <v>27</v>
+      </c>
+      <c r="T6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" s="2" customFormat="1" spans="1:20">
+      <c r="A7" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" s="7">
+        <v>0</v>
+      </c>
+      <c r="L7" s="7">
+        <v>1</v>
+      </c>
+      <c r="M7" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="N7" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1"/>
+      <c r="S7" t="s">
+        <v>37</v>
+      </c>
+      <c r="T7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="A8" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K8" s="7">
+        <v>0</v>
+      </c>
+      <c r="L8" s="7">
+        <v>1</v>
+      </c>
+      <c r="M8" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="S8" t="s">
+        <v>37</v>
+      </c>
+      <c r="T8" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:T8" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
